--- a/artfynd/A 547-2026 artfynd.xlsx
+++ b/artfynd/A 547-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3256205</v>
+        <v>93545215</v>
       </c>
       <c r="B2" t="n">
-        <v>107951</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104803</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221049</v>
+        <v>220461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Valeriana dioica</t>
+          <t>Cardamine flexuosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>With.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skrubbeboda jättegryta, Bl</t>
+          <t>Skrubbeboda, Bl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480271.9771066611</v>
+        <v>480309</v>
       </c>
       <c r="R2" t="n">
-        <v>6242108.874967681</v>
+        <v>6242122</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-06-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-06-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,12 +766,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Fuktig blandskog</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -790,22 +783,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ivar Björegren</t>
+          <t>Ivar Björegren, Sigbritt Björegren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>85265224</v>
+        <v>3256205</v>
       </c>
       <c r="B3" t="n">
-        <v>107952</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>111129</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,19 +819,24 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skrubbeboda jättegryta, Bl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480235.4947600315</v>
+        <v>480272</v>
       </c>
       <c r="R3" t="n">
-        <v>6242148.963159292</v>
+        <v>6242109</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,29 +858,14 @@
           <t>Kyrkhult</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>K-Olo-0403</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
           <t>2010-06-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2010-06-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,22 +877,227 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Fuktig blandskog</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Ivar Björegren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ivar Björegren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>85265224</v>
+      </c>
+      <c r="B4" t="n">
+        <v>111129</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Småvänderot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Valeriana dioica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skrubbeboda jättegryta, Bl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>480235</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6242149</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Olofström</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kyrkhult</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>K-Olo-0403</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2010-06-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2010-06-27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Åke Widgren</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Ivar Björegren</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6221970</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skrubbeboda, jättegrytor, Bl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>480269</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6242093</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Olofström</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kyrkhult</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2010-04-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2010-04-05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Bäck</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ivar Björegren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ivar Björegren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 547-2026 artfynd.xlsx
+++ b/artfynd/A 547-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93545215</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3256205</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85265224</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,8 +1118,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6221970</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>